--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G226"/>
+  <dimension ref="A1:G257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Data Engineer - AWS Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
+          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
+          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>AI  ML Engineer R&amp;D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
+          <t>https://www.indeed.com/viewjob?jk=93f6b234465478ea</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Frontend Software Engineer, SMTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Cloud Security</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=16091735f67f165f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,129 +1966,129 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Sr IT Engineer Cloud Security</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Network Monitoring Analyst</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,77 +3356,77 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Network Monitoring Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,15 +3488,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect and Data Engineer</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Numerica Credit Union</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,42 +4021,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,34 +7206,34 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Software Engineering Intern - DRC Team</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>StockX</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, DynamoDB, Splunk</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b144a0f72c9e40</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,32 +7496,32 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7531,32 +7531,32 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7566,32 +7566,32 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7601,32 +7601,32 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,32 +7636,32 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,32 +7671,32 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,32 +7706,32 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,32 +7741,32 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,67 +7776,67 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,32 +7846,32 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Solutions Architect (NYC)</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7881,32 +7881,32 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Solutions Architect (Dallas)</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7916,32 +7916,32 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Solutions Architect (Austin)</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7951,32 +7951,32 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,32 +7986,32 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,32 +8021,32 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,32 +8056,32 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,32 +8091,32 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Senior Technical Data Analyst</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>GHX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Scala, Polars, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,32 +8126,32 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,32 +8161,32 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,32 +8196,32 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0af3bdc55914e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,32 +8231,32 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8266,32 +8266,32 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,42 +8301,1127 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Snowflake Admin-7</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>NATIONMIND LLC</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Data Ops Engineer-6</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Python / Linux-6</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>IT Compliance Consultant</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>IT Data Solutions Developer Senior</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>HARBIN CLINIC</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Specialist, Data Engineer - NF</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Milford, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Shopko Optical</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Green Bay, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Analytics Migration Engineer</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>OneMagnify</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>California State Personnel Board</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Production Engineer</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Placer.ai</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Solutions Architect (NYC)</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Solutions Architect (Dallas)</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Solutions Architect (Austin)</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Claims Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer(Azure + Python)</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Intermediate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>REN</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>OIPA Engineer-6</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Data Analyst_EDM-7</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Teradata Developer-6</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
           <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Luxoft</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D226" t="n">
+      <c r="D256" t="n">
         <v>10.4</v>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Java Developer - Big Data Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=afd16380a8a7beef</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Cloud Security</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr IT Engineer Cloud Security</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
@@ -8763,17 +8763,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,24 +8861,24 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8896,24 +8896,24 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8931,24 +8931,24 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -8966,24 +8966,24 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9001,24 +9001,24 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Solutions Architect (NYC)</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9036,14 +9036,14 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Solutions Architect (Dallas)</t>
+          <t>Solutions Architect (NYC)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9071,14 +9071,14 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Solutions Architect (Austin)</t>
+          <t>Solutions Architect (Dallas)</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9106,24 +9106,24 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
+          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Solutions Architect (Austin)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9141,24 +9141,24 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9176,24 +9176,24 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9211,24 +9211,24 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9246,24 +9246,24 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9281,14 +9281,14 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9316,14 +9316,14 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9351,24 +9351,24 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9386,24 +9386,24 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9411,15 +9411,50 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Sr. Frontend Software Engineer, SMTS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Frontend Software Engineer, SMTS</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Cloud Security</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,69 +2061,69 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Sr IT Engineer Cloud Security</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Network Monitoring Analyst</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Network Monitoring Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,69 +3531,69 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,32 +6971,32 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,32 +7006,32 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,17 +7486,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,24 +8571,24 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,32 +8721,32 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,32 +8756,32 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,24 +8791,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,34 +8816,34 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,24 +8861,24 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8896,24 +8896,24 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8931,24 +8931,24 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -8966,24 +8966,24 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9001,24 +9001,24 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9036,24 +9036,24 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Solutions Architect (NYC)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9071,24 +9071,24 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Solutions Architect (Dallas)</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9106,24 +9106,24 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Solutions Architect (Austin)</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9141,24 +9141,24 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9176,19 +9176,19 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Solutions Architect (NYC)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9211,24 +9211,24 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Solutions Architect (Dallas)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9246,24 +9246,24 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Solutions Architect (Austin)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9281,24 +9281,24 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9316,14 +9316,14 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9351,24 +9351,24 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9386,24 +9386,24 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -9421,24 +9421,24 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9446,15 +9446,190 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Data Analyst_EDM-7</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Teradata Developer-6</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (AWS)</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Oracle PL/SQL Developer</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Career Mentors</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Addison, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G263"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Frontend Software Engineer, SMTS</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Sr. Frontend Software Engineer, SMTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16091735f67f165f</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr IT Engineer Cloud Security</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,69 +2061,69 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Cloud Security</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Network Monitoring Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Network Monitoring Analyst</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,69 +3531,69 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,59 +4206,59 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,32 +7006,32 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,17 +7486,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
@@ -8553,17 +8553,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,34 +8571,34 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,14 +8651,14 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,24 +8721,24 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,59 +8756,59 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,34 +8816,34 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,24 +8861,24 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8896,24 +8896,24 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8966,24 +8966,24 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9001,24 +9001,24 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9036,24 +9036,24 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9071,24 +9071,24 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9106,24 +9106,24 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9141,24 +9141,24 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Solutions Architect (NYC)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9176,14 +9176,14 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Solutions Architect (NYC)</t>
+          <t>Solutions Architect (Dallas)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,14 +9211,14 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
+          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Solutions Architect (Dallas)</t>
+          <t>Solutions Architect (Austin)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9246,24 +9246,24 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Solutions Architect (Austin)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9281,24 +9281,24 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9351,24 +9351,24 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9386,24 +9386,24 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -9421,14 +9421,14 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -9491,24 +9491,24 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -9526,24 +9526,24 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9551,34 +9551,34 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -9586,50 +9586,15 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Sr. Frontend Software Engineer, SMTS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Frontend Software Engineer, SMTS</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Cloud Security</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,69 +2061,69 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Sr IT Engineer Cloud Security</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Network Monitoring Analyst</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Network Monitoring Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
         </is>
       </c>
     </row>
@@ -3548,25 +3548,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
@@ -4143,60 +4143,60 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,32 +6971,32 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,14 +7006,14 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,17 +7486,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,34 +8501,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,14 +8651,14 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,59 +8721,59 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,34 +8781,34 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,24 +8861,24 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8931,24 +8931,24 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -8966,24 +8966,24 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9001,24 +9001,24 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9036,24 +9036,24 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9071,24 +9071,24 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9106,24 +9106,24 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Solutions Architect (NYC)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9141,14 +9141,14 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Solutions Architect (NYC)</t>
+          <t>Solutions Architect (Dallas)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9176,14 +9176,14 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
+          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Solutions Architect (Dallas)</t>
+          <t>Solutions Architect (Austin)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -9211,24 +9211,24 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Solutions Architect (Austin)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9246,24 +9246,24 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9281,24 +9281,24 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9351,24 +9351,24 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9386,14 +9386,14 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -9421,24 +9421,24 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -9456,24 +9456,24 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -9481,34 +9481,34 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -9526,24 +9526,24 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -9551,50 +9551,15 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI  ML Engineer R&amp;D</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, Vertex AI, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f6b234465478ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Java Developer - Big Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd16380a8a7beef</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,85 +1703,85 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Frontend Software Engineer, SMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c082bebcc2942a42</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
@@ -1983,11 +1983,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1996,134 +1996,134 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Cloud Security</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1df9c34d78ae7c</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,147 +3321,147 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Network Monitoring Analyst</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fdde3e56987d98</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,32 +6621,32 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,32 +6656,32 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,32 +6691,32 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,32 +6726,32 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,34 +7171,34 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,17 +7416,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,24 +8231,24 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,24 +8301,24 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8336,67 +8336,67 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,32 +8406,32 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,32 +8441,32 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,67 +8476,67 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,32 +8546,32 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,32 +8581,32 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,32 +8616,32 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,32 +8651,32 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,24 +8721,24 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,34 +8746,34 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,24 +8791,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,24 +8861,24 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8896,24 +8896,24 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8931,24 +8931,24 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -8966,24 +8966,24 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9001,24 +9001,24 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9026,542 +9026,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>California State Personnel Board</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Production Engineer</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Placer.ai</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Solutions Architect (NYC)</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf63b16ef347e97</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Dallas)</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc56922d5df7f41c</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Austin)</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a43fce5427236395</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Intermediate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>REN</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Data Analyst_EDM-7</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Teradata Developer-6</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (AWS)</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Oracle PL/SQL Developer</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Career Mentors</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>OIPA Engineer-6</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
+          <t>https://www.indeed.com/viewjob?jk=176be754bb6a10a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176be754bb6a10a9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Data Engineer - AWS Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
+          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
+          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,77 +1633,77 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,94 +3261,94 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Contractor - Senior Python Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,32 +6481,32 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,32 +6516,32 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,67 +8161,67 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,32 +8231,32 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8266,32 +8266,32 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,32 +8301,32 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,24 +8721,24 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,14 +8756,14 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,24 +8791,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,190 +8851,15 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>OIPA Engineer-6</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Data Analyst_EDM-7</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Teradata Developer-6</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (AWS)</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Oracle PL/SQL Developer</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Career Mentors</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Data Engineer - AWS Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
+          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
+          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
@@ -6838,17 +6838,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,59 +8161,59 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,34 +8221,34 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,24 +8301,24 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,34 +8326,34 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,24 +8721,24 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,14 +8756,14 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,24 +8791,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,15 +8851,85 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (AWS)</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Oracle PL/SQL Developer</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Career Mentors</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Addison, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
           <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="F243" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G243" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,69 +3216,69 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Contractor - Senior Python Developer</t>
+          <t>Senior Sales Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>MicroStrategy</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=63f6b81d553d195c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Contractor - Senior Python Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,24 +8161,24 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,59 +8196,59 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,34 +8256,34 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,24 +8301,24 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,34 +8326,34 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,24 +8721,24 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,24 +8756,24 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,14 +8791,14 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8826,14 +8826,14 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8861,24 +8861,24 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G243"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3233,52 +3233,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Contractor - Senior Python Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MicroStrategy</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63f6b81d553d195c</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Contractor - Senior Python Developer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,32 +6411,32 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,19 +6866,19 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6891,24 +6891,24 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,67 +8161,67 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,24 +8231,24 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,34 +8256,34 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,34 +8291,34 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,14 +8686,14 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,24 +8721,24 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,24 +8756,24 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -8791,24 +8791,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -8816,120 +8816,15 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Data Analyst_EDM-7</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Teradata Developer-6</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Oracle PL/SQL Developer</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Career Mentors</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
+          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,59 +3576,59 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Contractor - Senior Python Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Contractor - Senior Python Developer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,17 +6996,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7951,24 +7951,24 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,34 +8046,34 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,59 +8126,59 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,34 +8186,34 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,24 +8231,24 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,34 +8256,34 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,34 +8291,34 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8511,24 +8511,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8546,24 +8546,24 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8581,24 +8581,24 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8616,24 +8616,24 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8651,24 +8651,24 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8686,14 +8686,14 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8721,14 +8721,14 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8756,24 +8756,24 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -8781,50 +8781,15 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Oracle PL/SQL Developer</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Career Mentors</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G239"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Contractor - Senior Python Developer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8909dbc39a2e3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,67 +4521,67 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,32 +5711,32 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,67 +5746,67 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,67 +5816,67 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,67 +5921,67 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>DIAMONDBACK ENERGY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,32 +6061,32 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,32 +6096,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,32 +6166,32 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,32 +6201,32 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,32 +6271,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,67 +6376,67 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,2315 +6481,40 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>SQL Database Administrator – Contract Position</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>BranCore Technologies</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>GOAL Academy</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Pueblo, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Fidelity Investments</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Westlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Fidelity Investments</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>AWS CloudOps Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Sbt Global</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>SQL Database Administrator</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Apollo Technology Solutions LLC</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Senior Host Security Validation &amp; Operations Engineer - Global Security Organization</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=563ec55e69d8d3c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Snowflake Admin-7</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>DS Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>NATIONMIND LLC</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Python / Linux-6</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Data Ops Engineer-6</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Software Architect - AI</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>IT Compliance Consultant</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>IT Data Solutions Developer Senior</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>HARBIN CLINIC</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Engineer II – Java / Node.js / Python</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>DS Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Specialist, Data Engineer - NF</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Nationwide Mutual Insurance Company</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Milford, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Guidewire</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>DIAMONDBACK ENERGY</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Imprint</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Imprint</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>jamf</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Shopko Optical</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Green Bay, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Analytics Migration Engineer</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>OneMagnify</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>California State Personnel Board</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>REN</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Intermediate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>OIPA Engineer-6</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Data Analyst_EDM-7</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Teradata Developer-6</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Oracle PL/SQL Developer</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Career Mentors</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
         </is>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS Engineer</t>
+          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cooperative Benefits Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
+          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Data Engineer - AWS Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
+          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HealthEZ</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthEZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf448bcd373bda6</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,139 +3251,139 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Software Architect - AI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,59 +5816,59 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - NF</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Milford, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Milford, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Oracle, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f873725db34d611</t>
         </is>
       </c>
     </row>
@@ -5968,12 +5968,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DIAMONDBACK ENERGY</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>IAM, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfe495858ee758f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,17 +6016,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
+          <t>https://www.indeed.com/viewjob?jk=55b79f7343d5683d</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Scala, MySQL, DynamoDB, NoSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1fed4744aae6b26a</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>NGC – Senior Software Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4d745706dd7f0bfc</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,14 +6306,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
@@ -6517,6 +6517,111 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d90e5af987e92f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Software Dev Engineer (Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Brillius</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Intermediate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Azure, NoSQL, ETL, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>OIPA Engineer-6</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-13.xlsx
+++ b/results/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>IAM Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176be754bb6a10a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec47adf429b46ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
+          <t>https://www.indeed.com/viewjob?jk=176be754bb6a10a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cooperative Benefits Group</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS Engineer</t>
+          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cooperative Benefits Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
+          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Data Engineer - AWS Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc87db6d4b2806</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>SOC Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Kafka, Kafka Connect, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=15df68fbec62ef76</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Systems Engineer Associate (Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,56 +1602,56 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e16e21814bb29</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7f2ead1511ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ad2157784d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0a10bbf774a786</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solution Architect – Revenue Management</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Solution Architect – Revenue Management</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8ad481ff92fde3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Inventory and POS Revenue Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>6 points</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
+          <t>https://www.indeed.com/viewjob?jk=98876225aee54bf1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
+          <t>https://www.indeed.com/viewjob?jk=605cc27cc00cb3e9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b732fc3d99e007ab</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
+          <t>https://www.indeed.com/viewjob?jk=636f6bd7a4607297</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9deee4f1264d19f5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4447644330c531</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=674c0df416c0f9a3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
+          <t>https://www.indeed.com/viewjob?jk=baa745d9934d5ee3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
+          <t>https://www.indeed.com/viewjob?jk=52f197073864a5f2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a9c179b77c53dd</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
+          <t>https://www.indeed.com/viewjob?jk=47c296ff828a1757</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
+          <t>https://www.indeed.com/viewjob?jk=b27d47a89d27eeaf</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa33b96a2a9074</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f70441bf7321d135</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
+          <t>https://www.indeed.com/viewjob?jk=022dcf5407531b8a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=14594d1c6db250ab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
+          <t>https://www.indeed.com/viewjob?jk=03df6a37ea9a8fff</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3adb4f41f16b1ea5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
+          <t>https://www.indeed.com/viewjob?jk=ece2db47da40faab</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7cef803349f3b3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
+          <t>https://www.indeed.com/viewjob?jk=b62e88fad67b974c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3f24c798655ae4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=b476b86502e2a822</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aad8b0796577a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=61e858694a70eeb0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
+          <t>https://www.indeed.com/viewjob?jk=0672f8329652f552</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e86b68d4a20cd6c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab670e6a63f534</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2511a9302b47cb7f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb735394fbf355e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5da33156d406c0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac4a2fd73951024</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a8d1f4903e04e9</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=45f285b3d6851ca5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7817547c738ce84</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=93e092dd02464c6c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Platform Architect</t>
+          <t>Senior Cloud &amp; Container Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
+          <t>https://www.indeed.com/viewjob?jk=a00cd1a3981b69d3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Photon, GCP, Spark, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,59 +3646,59 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Oishii Farm Corporation</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Phillipsburg, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
+          <t>https://www.indeed.com/viewjob?jk=0837c0e67ad3e024</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oishii Farm Corporation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Phillipsburg, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c579ce0ad79d93a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
+          <t>https://www.indeed.com/viewjob?jk=062e6ece054461e0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
+          <t>https://www.indeed.com/viewjob?jk=af645fa575dd9b23</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecd6a3ff190637c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=d44012d3da71eb94</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
+          <t>https://www.indeed.com/viewjob?jk=d887e344ed3131e4</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
+          <t>https://www.indeed.com/viewjob?jk=965cd30d3d468a22</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=f34b1810aee62ca6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4476dd51ee8a68</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb691cc9ed5438c8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Dimensional Modeling, Kimball, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,102 +4206,102 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
+          <t>https://www.indeed.com/viewjob?jk=6b346f287e64bf41</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
+          <t>https://www.indeed.com/viewjob?jk=336e36d6061a7526</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Identity Security Fundamentals Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
+          <t>https://www.indeed.com/viewjob?jk=8000855936bcf0a2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SQL Database Administrator – Contract Position</t>
+          <t>Senior Software Engineer - LexisNexis</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GOAL Academy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pueblo, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS CloudOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>SQL Database Administrator – Contract Position</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7e8d0261fb47d1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (DEANG) Closing 3/22/2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NATIONMIND LLC</t>
+          <t>GOAL Academy</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pueblo, CO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3efe04557b32b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9899bc3a76c29241</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=edef1dab7d1ad9f6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Architect - AI</t>
+          <t>DevOps Engineer / Platform Engineer- Kubernetes / AWS / EKS / AKS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6e9f1e59377606</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b6d7d9bef7e9a5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>AWS CloudOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=49f68ec3b863323c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3f169e508b6cc4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Aires</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=93069cfd49e3bf96</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.